--- a/static/user_data.xlsx
+++ b/static/user_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarsitihanaf\Desktop\PROJECT\BE_DEV_DAHSBOARD\Dashboard\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B630E2D-B2B8-4440-B6B9-E2C378F4B102}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1760BEDE-F5CB-4D14-B67E-47523C283353}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="320">
   <si>
     <t>User_ID</t>
   </si>
@@ -38,16 +38,966 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>sarsitihanaf</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>sitihanafinilam.sari@Infineon.com</t>
+  </si>
+  <si>
+    <t>Hardians</t>
+  </si>
+  <si>
+    <t>Pranoto</t>
+  </si>
+  <si>
+    <t>Rahmad.Hardiansyah@infineon.com</t>
+  </si>
+  <si>
+    <t>Catur.Pranoto@infineon.com</t>
+  </si>
+  <si>
+    <t>AisyafitriAi</t>
+  </si>
+  <si>
+    <t>AzizahBellaN</t>
+  </si>
+  <si>
+    <t>Bahadi</t>
+  </si>
+  <si>
+    <t>FirdausFirda</t>
+  </si>
+  <si>
+    <t>Gemilang</t>
+  </si>
+  <si>
+    <t>HasibuanInda</t>
+  </si>
+  <si>
+    <t>JamiMuhammad</t>
+  </si>
+  <si>
+    <t>Kriswant</t>
+  </si>
+  <si>
+    <t>LeyleyAngela</t>
+  </si>
+  <si>
+    <t>MalasariKumi</t>
+  </si>
+  <si>
+    <t>Oktorina</t>
+  </si>
+  <si>
+    <t>PanggabeanGr</t>
+  </si>
+  <si>
+    <t>Prawoto</t>
+  </si>
+  <si>
+    <t>RRusli</t>
+  </si>
+  <si>
+    <t>Rifnaldi</t>
+  </si>
+  <si>
+    <t>Saefudin</t>
+  </si>
+  <si>
+    <t>SaefullahMal</t>
+  </si>
+  <si>
+    <t>Saepulloh</t>
+  </si>
+  <si>
+    <t>Sutambit</t>
+  </si>
+  <si>
+    <t>Sutikno</t>
+  </si>
+  <si>
+    <t>TovikTovik</t>
+  </si>
+  <si>
+    <t>Sikumban</t>
+  </si>
+  <si>
+    <t>Firdaus.Firdaus@infineon.com</t>
+  </si>
+  <si>
+    <t>Ledy.Gemilang@infineon.com</t>
+  </si>
+  <si>
+    <t>IndahHolijah.Hasibuan@infineon.com</t>
+  </si>
+  <si>
+    <t>Muhammad.Jamil@infineon.com</t>
+  </si>
+  <si>
+    <t>Heri.Kriswanto@infineon.com</t>
+  </si>
+  <si>
+    <t>AngelaGratiaCarolina.Leyley@infineon.com</t>
+  </si>
+  <si>
+    <t>Kumita.Malasari@infineon.com</t>
+  </si>
+  <si>
+    <t>Asfi.Oktorinal@infineon.com</t>
+  </si>
+  <si>
+    <t>GreaceHannaRosalina.Panggabean@infineon.com</t>
+  </si>
+  <si>
+    <t>BayuPrasetyoEko.Prawoto@infineon.com</t>
+  </si>
+  <si>
+    <t>Rusli.R@infineon.com</t>
+  </si>
+  <si>
+    <t>Rifnaldi.Rifnaldi@infineon.com</t>
+  </si>
+  <si>
+    <t>Faik.Saefudin@infineon.com</t>
+  </si>
+  <si>
+    <t>Malik.Saefullah@infineon.com</t>
+  </si>
+  <si>
+    <t>Eep.Saepulloh@infineon.com</t>
+  </si>
+  <si>
+    <t>Sutambit.Sutambit@infineon.com</t>
+  </si>
+  <si>
+    <t>Heri.Sutikno@infineon.com</t>
+  </si>
+  <si>
+    <t>Tovik.Tovik@infineon.com</t>
+  </si>
+  <si>
+    <t>Wardion.Wardion@infineon.com</t>
+  </si>
+  <si>
+    <t>Aisyafitri.Aisyafitri@infineon.com</t>
+  </si>
+  <si>
+    <t>BellaNur.Azizah@infineon.com</t>
+  </si>
+  <si>
+    <t>Bahadi.Bahadi@infineon.com</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>INFINEON</t>
+  </si>
+  <si>
+    <t>Widhiasih</t>
+  </si>
+  <si>
+    <t>VasquezRamil</t>
+  </si>
+  <si>
+    <t>Uyao</t>
+  </si>
+  <si>
+    <t>Regua</t>
+  </si>
+  <si>
+    <t>Rachmadi</t>
+  </si>
+  <si>
+    <t>PutraTeu</t>
+  </si>
+  <si>
+    <t>Poon</t>
+  </si>
+  <si>
+    <t>PakpahaBrian</t>
+  </si>
+  <si>
+    <t>Olandag</t>
+  </si>
+  <si>
+    <t>NarayaJa</t>
+  </si>
+  <si>
+    <t>CManaois</t>
+  </si>
+  <si>
+    <t>LauntuH</t>
+  </si>
+  <si>
+    <t>LandichoJean</t>
+  </si>
+  <si>
+    <t>Laela</t>
+  </si>
+  <si>
+    <t>Kelana</t>
+  </si>
+  <si>
+    <t>Hidlao</t>
+  </si>
+  <si>
+    <t>Firmansyah</t>
+  </si>
+  <si>
+    <t>FadilaAnnisa</t>
+  </si>
+  <si>
+    <t>Elambre</t>
+  </si>
+  <si>
+    <t>DelRosaV</t>
+  </si>
+  <si>
+    <t>DeOcampo</t>
+  </si>
+  <si>
+    <t>DannyKoh</t>
+  </si>
+  <si>
+    <t>Casicas</t>
+  </si>
+  <si>
+    <t>BilaShifaSal</t>
+  </si>
+  <si>
+    <t>AzizaHasnaHa</t>
+  </si>
+  <si>
+    <t>AsisRona</t>
+  </si>
+  <si>
+    <t>ArianiH</t>
+  </si>
+  <si>
+    <t>Gati.Widhiasih@infineon.com</t>
+  </si>
+  <si>
+    <t>RamilNasalga.Vasquez@infineon.com</t>
+  </si>
+  <si>
+    <t>ChristianJayAndal.Uyao@infineon.com</t>
+  </si>
+  <si>
+    <t>Clemen.Regua@infineon.com</t>
+  </si>
+  <si>
+    <t>Arbiyoto.Rachmadi@infineon.com</t>
+  </si>
+  <si>
+    <t>TeukuAlvianRisiana.Putra@infineon.com</t>
+  </si>
+  <si>
+    <t>YuanPuoh.Poon@infineon.com</t>
+  </si>
+  <si>
+    <t>Brian.Pakpahan@infineon.com</t>
+  </si>
+  <si>
+    <t>ChristoperTinao.Olandag@infineon.com</t>
+  </si>
+  <si>
+    <t>Jayaganasan.Narayanasamy@infineon.com</t>
+  </si>
+  <si>
+    <t>Joel.Manaois@infineon.com</t>
+  </si>
+  <si>
+    <t>Hazis.Launtu@infineon.com</t>
+  </si>
+  <si>
+    <t>JeanetteKalalo.Landicho@infineon.com</t>
+  </si>
+  <si>
+    <t>Dian.Laela@infineon.com</t>
+  </si>
+  <si>
+    <t>Afandi.Kelana@infineon.com</t>
+  </si>
+  <si>
+    <t>ArnelJose.Hidlao@infineon.com</t>
+  </si>
+  <si>
+    <t>KhoirilMetrima.Firmansyah@infineon.com</t>
+  </si>
+  <si>
+    <t>AnnisaDhiya.Fadila@infineon.com</t>
+  </si>
+  <si>
+    <t>EugenioEterno.Elambre@infineon.com</t>
+  </si>
+  <si>
+    <t>VictorCruz.DelRosario@infineon.com</t>
+  </si>
+  <si>
+    <t>PaulGilbertCalabio.DeOcampo@infineon.com</t>
+  </si>
+  <si>
+    <t>CherHau.DannyKoh@infineon.com</t>
+  </si>
+  <si>
+    <t>BryanLimpio.Casicas@infineon.com</t>
+  </si>
+  <si>
+    <t>ShifaSalsa.Bila@infineon.com</t>
+  </si>
+  <si>
+    <t>HasnaHaifa.Azizah@infineon.com</t>
+  </si>
+  <si>
+    <t>RonanCanonizado.Asis@infineon.com</t>
+  </si>
+  <si>
+    <t>Hanna.Ariani@infineon.com</t>
+  </si>
+  <si>
+    <t>Adepi</t>
+  </si>
+  <si>
+    <t>Ivanna</t>
+  </si>
+  <si>
+    <t>PutriAmorDis</t>
+  </si>
+  <si>
+    <t>Rahmadha</t>
+  </si>
+  <si>
+    <t>ChristiadiS</t>
+  </si>
+  <si>
+    <t>Surbakti</t>
+  </si>
+  <si>
+    <t>WinataHandik</t>
+  </si>
+  <si>
+    <t>HandikaEki.Winata@infineon.com</t>
+  </si>
+  <si>
+    <t>KamarulZaman.Surbakti@infineon.com</t>
+  </si>
+  <si>
+    <t>Adrian.ChristiadiS@infineon.com</t>
+  </si>
+  <si>
+    <t>Syahril.Rahmadhani@infineon.com</t>
+  </si>
+  <si>
+    <t>AmorDisha.Putri@infineon.com</t>
+  </si>
+  <si>
+    <t>FaidzaDwi.Ivanna@infineon.com</t>
+  </si>
+  <si>
+    <t>Adepi.Adepi@infineon.com</t>
+  </si>
+  <si>
+    <t>ZhouYira</t>
+  </si>
+  <si>
+    <t>YuAlfredoJrT</t>
+  </si>
+  <si>
+    <t>YongKhai</t>
+  </si>
+  <si>
+    <t>YeQ</t>
+  </si>
+  <si>
+    <t>YapFelic</t>
+  </si>
+  <si>
+    <t>YanKai</t>
+  </si>
+  <si>
+    <t>WongTeuk</t>
+  </si>
+  <si>
+    <t>Yazid</t>
+  </si>
+  <si>
+    <t>Tye</t>
+  </si>
+  <si>
+    <t>Tongson</t>
+  </si>
+  <si>
+    <t>TeoPo</t>
+  </si>
+  <si>
+    <t>Tangaha</t>
+  </si>
+  <si>
+    <t>JustinTa</t>
+  </si>
+  <si>
+    <t>TanChihEngNa</t>
+  </si>
+  <si>
+    <t>TanL</t>
+  </si>
+  <si>
+    <t>TanWan</t>
+  </si>
+  <si>
+    <t>TaiKeenC</t>
+  </si>
+  <si>
+    <t>Susilo</t>
+  </si>
+  <si>
+    <t>SungaMar</t>
+  </si>
+  <si>
+    <t>SugiriAn</t>
+  </si>
+  <si>
+    <t>Sudibya</t>
+  </si>
+  <si>
+    <t>SuZiwei</t>
+  </si>
+  <si>
+    <t>RodrigSh</t>
+  </si>
+  <si>
+    <t>RodriguezJen</t>
+  </si>
+  <si>
+    <t>ReynosoD</t>
+  </si>
+  <si>
+    <t>RenWeiwe</t>
+  </si>
+  <si>
+    <t>QuahSiew</t>
+  </si>
+  <si>
+    <t>MercaMar</t>
+  </si>
+  <si>
+    <t>PenaValRudol</t>
+  </si>
+  <si>
+    <t>OoiSengY</t>
+  </si>
+  <si>
+    <t>OngRyan</t>
+  </si>
+  <si>
+    <t>Ngiow</t>
+  </si>
+  <si>
+    <t>NgBeepoh</t>
+  </si>
+  <si>
+    <t>NgTh</t>
+  </si>
+  <si>
+    <t>NeoChinYong</t>
+  </si>
+  <si>
+    <t>NataraRa</t>
+  </si>
+  <si>
+    <t>MuellerTimoM</t>
+  </si>
+  <si>
+    <t>MohdPadz</t>
+  </si>
+  <si>
+    <t>MatNoorAkmal</t>
+  </si>
+  <si>
+    <t>MarimuthuPan</t>
+  </si>
+  <si>
+    <t>Mahabayu</t>
+  </si>
+  <si>
+    <t>LowY</t>
+  </si>
+  <si>
+    <t>LongH</t>
+  </si>
+  <si>
+    <t>LohJansi</t>
+  </si>
+  <si>
+    <t>LohKhaiM</t>
+  </si>
+  <si>
+    <t>LYu</t>
+  </si>
+  <si>
+    <t>LimLayH</t>
+  </si>
+  <si>
+    <t>LimSock</t>
+  </si>
+  <si>
+    <t>LimShaw</t>
+  </si>
+  <si>
+    <t>LeeC</t>
+  </si>
+  <si>
+    <t>LeeL</t>
+  </si>
+  <si>
+    <t>LeeLi</t>
+  </si>
+  <si>
+    <t>LauH</t>
+  </si>
+  <si>
+    <t>LauY</t>
+  </si>
+  <si>
+    <t>Lau</t>
+  </si>
+  <si>
+    <t>LauYewAnnAnd</t>
+  </si>
+  <si>
+    <t>LamDuongHoan</t>
+  </si>
+  <si>
+    <t>LamMi</t>
+  </si>
+  <si>
+    <t>KumarDharmes</t>
+  </si>
+  <si>
+    <t>KooKokki</t>
+  </si>
+  <si>
+    <t>KongF</t>
+  </si>
+  <si>
+    <t>KohL</t>
+  </si>
+  <si>
+    <t>KanChanW</t>
+  </si>
+  <si>
+    <t>MathewJo</t>
+  </si>
+  <si>
+    <t>Holgado</t>
+  </si>
+  <si>
+    <t>HoHongMe</t>
+  </si>
+  <si>
+    <t>HeJiabe</t>
+  </si>
+  <si>
+    <t>HawCheeP</t>
+  </si>
+  <si>
+    <t>GohW</t>
+  </si>
+  <si>
+    <t>GargN</t>
+  </si>
+  <si>
+    <t>GaballoJ</t>
+  </si>
+  <si>
+    <t>FatyLina</t>
+  </si>
+  <si>
+    <t>ChueLarr</t>
+  </si>
+  <si>
+    <t>ChChoonW</t>
+  </si>
+  <si>
+    <t>ChCheeKe</t>
+  </si>
+  <si>
+    <t>ChongKo</t>
+  </si>
+  <si>
+    <t>ChongKokW</t>
+  </si>
+  <si>
+    <t>Cheong</t>
+  </si>
+  <si>
+    <t>ChengYu</t>
+  </si>
+  <si>
+    <t>ChenZhao</t>
+  </si>
+  <si>
+    <t>CheamHingSua</t>
+  </si>
+  <si>
+    <t>ChangSeo</t>
+  </si>
+  <si>
+    <t>ChaiFuij</t>
+  </si>
+  <si>
+    <t>CastilloRonn</t>
+  </si>
+  <si>
+    <t>Cando</t>
+  </si>
+  <si>
+    <t>Bartolo</t>
+  </si>
+  <si>
+    <t>Arnesto</t>
+  </si>
+  <si>
+    <t>AndrianiYose</t>
+  </si>
+  <si>
+    <t>Acuesta</t>
+  </si>
+  <si>
+    <t>Acquiata</t>
+  </si>
+  <si>
+    <t>AbdulSit</t>
+  </si>
+  <si>
+    <t>Stella.Zhou@infineon.com</t>
+  </si>
+  <si>
+    <t>AlfredoJrTizon.Yu@infineon.com</t>
+  </si>
+  <si>
+    <t>KhaiSeen.Yong@infineon.com</t>
+  </si>
+  <si>
+    <t>Qun.Ye@infineon.com</t>
+  </si>
+  <si>
+    <t>FeliciaEstorioso.Yap@infineon.com</t>
+  </si>
+  <si>
+    <t>Kai.Yang@infineon.com</t>
+  </si>
+  <si>
+    <t>TeukChuenRonald.Wong@infineon.com</t>
+  </si>
+  <si>
+    <t>Mohamad.Yazid@infineon.com</t>
+  </si>
+  <si>
+    <t>Ching-Yun.Tye@infineon.com</t>
+  </si>
+  <si>
+    <t>MonicaSabino.Tongson@infineon.com</t>
+  </si>
+  <si>
+    <t>PoiSiong.Teo@infineon.com</t>
+  </si>
+  <si>
+    <t>DennisMata.Tangaha@infineon.com</t>
+  </si>
+  <si>
+    <t>KhaiYap.JustinTan@infineon.com</t>
+  </si>
+  <si>
+    <t>ChihEngNathanael.Tan@infineon.com</t>
+  </si>
+  <si>
+    <t>LanChu.Tan-EE@infineon.com</t>
+  </si>
+  <si>
+    <t>WanLin.Tan@infineon.com</t>
+  </si>
+  <si>
+    <t>KeenChee.Tai@infineon.com</t>
+  </si>
+  <si>
+    <t>Eko.Susilo@infineon.com</t>
+  </si>
+  <si>
+    <t>MariaLourdesDavid.Sunga@infineon.com</t>
+  </si>
+  <si>
+    <t>Anton.Sugiri@infineon.com</t>
+  </si>
+  <si>
+    <t>IDewaMadeAnom.Sudibya@infineon.com</t>
+  </si>
+  <si>
+    <t>Ziwei.Su@infineon.com</t>
+  </si>
+  <si>
+    <t>SheilaDimol.Rodriguez@infineon.com</t>
+  </si>
+  <si>
+    <t>JenelynSimbulan.Rodriguez@infineon.com</t>
+  </si>
+  <si>
+    <t>DexterInciong.Reynoso@infineon.com</t>
+  </si>
+  <si>
+    <t>Weiwei.Ren@infineon.com</t>
+  </si>
+  <si>
+    <t>SiewEng.Quah@infineon.com</t>
+  </si>
+  <si>
+    <t>MaryGrace.Mercado2@infineon.com</t>
+  </si>
+  <si>
+    <t>ValRudolfBumalay.Pena@infineon.com</t>
+  </si>
+  <si>
+    <t>SengYeong.Ooi@infineon.com</t>
+  </si>
+  <si>
+    <t>ChenHo.Ong@infineon.com</t>
+  </si>
+  <si>
+    <t>ShinTat.Ngiow@infineon.com</t>
+  </si>
+  <si>
+    <t>Christine.Ng@infineon.com</t>
+  </si>
+  <si>
+    <t>shirley.ng@infineon.com</t>
+  </si>
+  <si>
+    <t>ChinYong.Neo@infineon.com</t>
+  </si>
+  <si>
+    <t>Subramanian.N@infineon.com</t>
+  </si>
+  <si>
+    <t>TimoMichael.Mueller@infineon.com</t>
+  </si>
+  <si>
+    <t>KhairulAnuar.MohdPadzil@infineon.com</t>
+  </si>
+  <si>
+    <t>AkmalHakimi.MatNoor@infineon.com</t>
+  </si>
+  <si>
+    <t>PandiChelvam.Marimuthu@infineon.com</t>
+  </si>
+  <si>
+    <t>Putu.Mada@infineon.com</t>
+  </si>
+  <si>
+    <t>YuNing.Low@infineon.com</t>
+  </si>
+  <si>
+    <t>Hazel.Long@infineon.com</t>
+  </si>
+  <si>
+    <t>JanSing.Loh@infineon.com</t>
+  </si>
+  <si>
+    <t>KhaiMing.Loh@infineon.com</t>
+  </si>
+  <si>
+    <t>Richard.Liu@infineon.com</t>
+  </si>
+  <si>
+    <t>Geraldine.Lim@infineon.com</t>
+  </si>
+  <si>
+    <t>Alexis.Lim@infineon.com</t>
+  </si>
+  <si>
+    <t>ShawFa.Lim@infineon.com</t>
+  </si>
+  <si>
+    <t>ChanHon.Lee@infineon.com</t>
+  </si>
+  <si>
+    <t>LiWen.Lee@infineon.com</t>
+  </si>
+  <si>
+    <t>LiChong.Lee@infineon.com</t>
+  </si>
+  <si>
+    <t>HongSeng.Lau@infineon.com</t>
+  </si>
+  <si>
+    <t>YingHung.Lau@infineon.com</t>
+  </si>
+  <si>
+    <t>Ghee-Yew.Lau@infineon.com</t>
+  </si>
+  <si>
+    <t>YewAnnAndrew.Lau@infineon.com</t>
+  </si>
+  <si>
+    <t>DuongHoangVu.Lam@infineon.com</t>
+  </si>
+  <si>
+    <t>MianMian.Lam@infineon.com</t>
+  </si>
+  <si>
+    <t>Dharmesh.Kumar@infineon.com</t>
+  </si>
+  <si>
+    <t>Kok-Kiat.Koo@infineon.com</t>
+  </si>
+  <si>
+    <t>Fanlei.Kong@infineon.com</t>
+  </si>
+  <si>
+    <t>LeyHow.Koh@infineon.com</t>
+  </si>
+  <si>
+    <t>Augustine.Kan@infineon.com</t>
+  </si>
+  <si>
+    <t>JoeMathew.John@infineon.com</t>
+  </si>
+  <si>
+    <t>ElmerSenorin.Holgado@infineon.com</t>
+  </si>
+  <si>
+    <t>HongMeng.Ho@infineon.com</t>
+  </si>
+  <si>
+    <t>Jiabei.He@infineon.com</t>
+  </si>
+  <si>
+    <t>CheePin.Haw@infineon.com</t>
+  </si>
+  <si>
+    <t>WeiJie.Goh@infineon.com</t>
+  </si>
+  <si>
+    <t>Nitin.Garg2@infineon.com</t>
+  </si>
+  <si>
+    <t>AmandoB.GaballoJr@infineon.com</t>
+  </si>
+  <si>
+    <t>Lina.Faty@infineon.com</t>
+  </si>
+  <si>
+    <t>SweeChin.Chue@infineon.com</t>
+  </si>
+  <si>
+    <t>ChoonWee.Chua@infineon.com</t>
+  </si>
+  <si>
+    <t>CheeKenPhilip.Chong@infineon.com</t>
+  </si>
+  <si>
+    <t>Alex.Chong@infineon.com</t>
+  </si>
+  <si>
+    <t>Eric.Chong@infineon.com</t>
+  </si>
+  <si>
+    <t>MaryAnnieQuezada.Cheong@infineon.com</t>
+  </si>
+  <si>
+    <t>YuSeng.Cheng@infineon.com</t>
+  </si>
+  <si>
+    <t>Zhaohui.Chen@infineon.com</t>
+  </si>
+  <si>
+    <t>Eric.Cheam@infineon.com</t>
+  </si>
+  <si>
+    <t>seow-pin.chang@infineon.com</t>
+  </si>
+  <si>
+    <t>Cynthia.Chai@infineon.com</t>
+  </si>
+  <si>
+    <t>RonnelPerez.Castillo@infineon.com</t>
+  </si>
+  <si>
+    <t>RogelioJrPincil.Cando@infineon.com</t>
+  </si>
+  <si>
+    <t>MarlonDavid.Bartolo@infineon.com</t>
+  </si>
+  <si>
+    <t>LaarniB.Arnesto@infineon.com</t>
+  </si>
+  <si>
+    <t>Yosephine.Andriani@infineon.com</t>
+  </si>
+  <si>
+    <t>Albert.Acuesta@infineon.com</t>
+  </si>
+  <si>
+    <t>EricBriones.Acquiatan@infineon.com</t>
+  </si>
+  <si>
+    <t>SitiMaznah.AbdulRahim@infineon.com</t>
+  </si>
+  <si>
+    <t>GultomWennyL</t>
+  </si>
+  <si>
+    <t>AlghifariDaf</t>
+  </si>
+  <si>
+    <t>Fitri</t>
+  </si>
+  <si>
+    <t>PakpahanBrie</t>
+  </si>
+  <si>
+    <t>RamadhanFikr</t>
+  </si>
+  <si>
+    <t>DaffaMaulana.Alghifari@infineon.com</t>
+  </si>
+  <si>
+    <t>Umniyyah.Fitri@infineon.com</t>
+  </si>
+  <si>
+    <t>WennyLestariBr.Gultom@infineon.com</t>
+  </si>
+  <si>
+    <t>Briel.Pakpahan@infineon.com</t>
+  </si>
+  <si>
+    <t>Fikri.Ramadhan@infineon.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -70,13 +1020,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -377,14 +1330,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -408,7 +1361,3265 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s">
+        <v>59</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" t="s">
+        <v>59</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" t="s">
+        <v>59</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>195</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>193</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D50" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D56" t="s">
+        <v>58</v>
+      </c>
+      <c r="E56" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D57" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D58" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D62" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>184</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>181</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D67" t="s">
+        <v>58</v>
+      </c>
+      <c r="E67" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>180</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D69" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" t="s">
+        <v>59</v>
+      </c>
+      <c r="F69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D70" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" t="s">
+        <v>59</v>
+      </c>
+      <c r="F70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" t="s">
+        <v>59</v>
+      </c>
+      <c r="F71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>177</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" t="s">
+        <v>59</v>
+      </c>
+      <c r="F72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" t="s">
+        <v>58</v>
+      </c>
+      <c r="E73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>176</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D74" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" t="s">
+        <v>59</v>
+      </c>
+      <c r="F74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D75" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>174</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D76" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D78" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D79" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" t="s">
+        <v>59</v>
+      </c>
+      <c r="F79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D80" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" t="s">
+        <v>59</v>
+      </c>
+      <c r="F80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D81" t="s">
+        <v>58</v>
+      </c>
+      <c r="E81" t="s">
+        <v>59</v>
+      </c>
+      <c r="F81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>168</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D82" t="s">
+        <v>58</v>
+      </c>
+      <c r="E82" t="s">
+        <v>59</v>
+      </c>
+      <c r="F82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" t="s">
+        <v>58</v>
+      </c>
+      <c r="E83" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>70</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" t="s">
+        <v>58</v>
+      </c>
+      <c r="E84" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D85" t="s">
+        <v>58</v>
+      </c>
+      <c r="E85" t="s">
+        <v>59</v>
+      </c>
+      <c r="F85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>166</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D86" t="s">
+        <v>58</v>
+      </c>
+      <c r="E86" t="s">
+        <v>59</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>165</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87" t="s">
+        <v>58</v>
+      </c>
+      <c r="E87" t="s">
+        <v>59</v>
+      </c>
+      <c r="F87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>164</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D88" t="s">
+        <v>58</v>
+      </c>
+      <c r="E88" t="s">
+        <v>59</v>
+      </c>
+      <c r="F88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>69</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E89" t="s">
+        <v>59</v>
+      </c>
+      <c r="F89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>163</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>162</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D91" t="s">
+        <v>58</v>
+      </c>
+      <c r="E91" t="s">
+        <v>59</v>
+      </c>
+      <c r="F91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>161</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D92" t="s">
+        <v>58</v>
+      </c>
+      <c r="E92" t="s">
+        <v>59</v>
+      </c>
+      <c r="F92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D93" t="s">
+        <v>58</v>
+      </c>
+      <c r="E93" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>159</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D94" t="s">
+        <v>58</v>
+      </c>
+      <c r="E94" t="s">
+        <v>59</v>
+      </c>
+      <c r="F94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95" t="s">
+        <v>58</v>
+      </c>
+      <c r="E95" t="s">
+        <v>59</v>
+      </c>
+      <c r="F95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>68</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D96" t="s">
+        <v>58</v>
+      </c>
+      <c r="E96" t="s">
+        <v>59</v>
+      </c>
+      <c r="F96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>158</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D97" t="s">
+        <v>58</v>
+      </c>
+      <c r="E97" t="s">
+        <v>59</v>
+      </c>
+      <c r="F97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>157</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D98" t="s">
+        <v>58</v>
+      </c>
+      <c r="E98" t="s">
+        <v>59</v>
+      </c>
+      <c r="F98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D99" t="s">
+        <v>58</v>
+      </c>
+      <c r="E99" t="s">
+        <v>59</v>
+      </c>
+      <c r="F99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" t="s">
+        <v>58</v>
+      </c>
+      <c r="E100" t="s">
+        <v>59</v>
+      </c>
+      <c r="F100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>156</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>155</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D102" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>66</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D103" t="s">
+        <v>58</v>
+      </c>
+      <c r="E103" t="s">
+        <v>59</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>58</v>
+      </c>
+      <c r="E104" t="s">
+        <v>59</v>
+      </c>
+      <c r="F104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>65</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D105" t="s">
+        <v>58</v>
+      </c>
+      <c r="E105" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D106" t="s">
+        <v>58</v>
+      </c>
+      <c r="E106" t="s">
+        <v>59</v>
+      </c>
+      <c r="F106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>154</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D107" t="s">
+        <v>58</v>
+      </c>
+      <c r="E107" t="s">
+        <v>59</v>
+      </c>
+      <c r="F107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" t="s">
+        <v>58</v>
+      </c>
+      <c r="E108" t="s">
+        <v>59</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>64</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D109" t="s">
+        <v>58</v>
+      </c>
+      <c r="E109" t="s">
+        <v>59</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>117</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D110" t="s">
+        <v>58</v>
+      </c>
+      <c r="E110" t="s">
+        <v>59</v>
+      </c>
+      <c r="F110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>63</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+      <c r="E111" t="s">
+        <v>59</v>
+      </c>
+      <c r="F111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" t="s">
+        <v>59</v>
+      </c>
+      <c r="F112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D113" t="s">
+        <v>58</v>
+      </c>
+      <c r="E113" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D114" t="s">
+        <v>58</v>
+      </c>
+      <c r="E114" t="s">
+        <v>59</v>
+      </c>
+      <c r="F114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D115" t="s">
+        <v>58</v>
+      </c>
+      <c r="E115" t="s">
+        <v>59</v>
+      </c>
+      <c r="F115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>150</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D116" t="s">
+        <v>58</v>
+      </c>
+      <c r="E116" t="s">
+        <v>59</v>
+      </c>
+      <c r="F116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" t="s">
+        <v>58</v>
+      </c>
+      <c r="E117" t="s">
+        <v>59</v>
+      </c>
+      <c r="F117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>29</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D118" t="s">
+        <v>58</v>
+      </c>
+      <c r="E118" t="s">
+        <v>59</v>
+      </c>
+      <c r="F118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D119" t="s">
+        <v>58</v>
+      </c>
+      <c r="E119" t="s">
+        <v>59</v>
+      </c>
+      <c r="F119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" t="s">
+        <v>58</v>
+      </c>
+      <c r="E120" t="s">
+        <v>59</v>
+      </c>
+      <c r="F120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>149</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D121" t="s">
+        <v>58</v>
+      </c>
+      <c r="E121" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>148</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D122" t="s">
+        <v>58</v>
+      </c>
+      <c r="E122" t="s">
+        <v>59</v>
+      </c>
+      <c r="F122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>147</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D123" t="s">
+        <v>58</v>
+      </c>
+      <c r="E123" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>146</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D124" t="s">
+        <v>58</v>
+      </c>
+      <c r="E124" t="s">
+        <v>59</v>
+      </c>
+      <c r="F124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>119</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D125" t="s">
+        <v>58</v>
+      </c>
+      <c r="E125" t="s">
+        <v>59</v>
+      </c>
+      <c r="F125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>145</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D126" t="s">
+        <v>58</v>
+      </c>
+      <c r="E126" t="s">
+        <v>59</v>
+      </c>
+      <c r="F126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D127" t="s">
+        <v>58</v>
+      </c>
+      <c r="E127" t="s">
+        <v>59</v>
+      </c>
+      <c r="F127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>33</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D128" t="s">
+        <v>58</v>
+      </c>
+      <c r="E128" t="s">
+        <v>59</v>
+      </c>
+      <c r="F128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>144</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D129" t="s">
+        <v>58</v>
+      </c>
+      <c r="E129" t="s">
+        <v>59</v>
+      </c>
+      <c r="F129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>143</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D130" t="s">
+        <v>58</v>
+      </c>
+      <c r="E130" t="s">
+        <v>59</v>
+      </c>
+      <c r="F130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D131" t="s">
+        <v>58</v>
+      </c>
+      <c r="E131" t="s">
+        <v>59</v>
+      </c>
+      <c r="F131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>141</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D132" t="s">
+        <v>58</v>
+      </c>
+      <c r="E132" t="s">
+        <v>59</v>
+      </c>
+      <c r="F132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>140</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D133" t="s">
+        <v>58</v>
+      </c>
+      <c r="E133" t="s">
+        <v>59</v>
+      </c>
+      <c r="F133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>139</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D134" t="s">
+        <v>58</v>
+      </c>
+      <c r="E134" t="s">
+        <v>59</v>
+      </c>
+      <c r="F134" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>138</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D135" t="s">
+        <v>58</v>
+      </c>
+      <c r="E135" t="s">
+        <v>59</v>
+      </c>
+      <c r="F135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>137</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D136" t="s">
+        <v>58</v>
+      </c>
+      <c r="E136" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>34</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D137" t="s">
+        <v>58</v>
+      </c>
+      <c r="E137" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>136</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D138" t="s">
+        <v>58</v>
+      </c>
+      <c r="E138" t="s">
+        <v>59</v>
+      </c>
+      <c r="F138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>62</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139" t="s">
+        <v>58</v>
+      </c>
+      <c r="E139" t="s">
+        <v>59</v>
+      </c>
+      <c r="F139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>61</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D140" t="s">
+        <v>58</v>
+      </c>
+      <c r="E140" t="s">
+        <v>59</v>
+      </c>
+      <c r="F140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>135</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D141" t="s">
+        <v>58</v>
+      </c>
+      <c r="E141" t="s">
+        <v>59</v>
+      </c>
+      <c r="F141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>35</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D142" t="s">
+        <v>58</v>
+      </c>
+      <c r="E142" t="s">
+        <v>59</v>
+      </c>
+      <c r="F142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>60</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D143" t="s">
+        <v>58</v>
+      </c>
+      <c r="E143" t="s">
+        <v>59</v>
+      </c>
+      <c r="F143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>120</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D144" t="s">
+        <v>58</v>
+      </c>
+      <c r="E144" t="s">
+        <v>59</v>
+      </c>
+      <c r="F144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>134</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D145" t="s">
+        <v>58</v>
+      </c>
+      <c r="E145" t="s">
+        <v>59</v>
+      </c>
+      <c r="F145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>133</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D146" t="s">
+        <v>58</v>
+      </c>
+      <c r="E146" t="s">
+        <v>59</v>
+      </c>
+      <c r="F146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>132</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D147" t="s">
+        <v>58</v>
+      </c>
+      <c r="E147" t="s">
+        <v>59</v>
+      </c>
+      <c r="F147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>131</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D148" t="s">
+        <v>58</v>
+      </c>
+      <c r="E148" t="s">
+        <v>59</v>
+      </c>
+      <c r="F148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>130</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D149" t="s">
+        <v>58</v>
+      </c>
+      <c r="E149" t="s">
+        <v>59</v>
+      </c>
+      <c r="F149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>129</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D150" t="s">
+        <v>58</v>
+      </c>
+      <c r="E150" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>128</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D151" t="s">
+        <v>58</v>
+      </c>
+      <c r="E151" t="s">
+        <v>59</v>
+      </c>
+      <c r="F151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>310</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D152" t="s">
+        <v>58</v>
+      </c>
+      <c r="E152" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>311</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D153" t="s">
+        <v>58</v>
+      </c>
+      <c r="E153" t="s">
+        <v>59</v>
+      </c>
+      <c r="F153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>312</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D154" t="s">
+        <v>58</v>
+      </c>
+      <c r="E154" t="s">
+        <v>59</v>
+      </c>
+      <c r="F154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>313</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D155" t="s">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>59</v>
+      </c>
+      <c r="F155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>314</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D156" t="s">
+        <v>58</v>
+      </c>
+      <c r="E156" t="s">
+        <v>59</v>
+      </c>
+      <c r="F156" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{AF7FEA75-43E1-45CA-8C15-F9F7F0CD386C}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{88FCFD4A-52E6-4175-BE48-09CD9E6E276E}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{3BE8B2EC-93C4-4C8D-9D74-6CAB6CE4226D}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{658FA2CF-6A95-4F52-8A79-004947E8955D}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{C4FCE219-A75C-4B40-837D-6477FC4C8AC8}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{8E63164D-138C-4623-B75A-2C0707B80ADE}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{4F53DE0D-AE4C-4936-9EB9-BD0CE3A74958}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{AED485FF-5A97-4E54-A161-1E73F016AEE1}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{57267280-3A8B-430B-93EF-88F846901B35}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{FF58BB63-F408-4FC2-A636-23B09926921D}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{AD504A00-3675-489D-82CF-B3381A0870F3}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{1D931C42-5397-49AA-A4C4-9E8F81E509FD}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{3C8EA787-DAD1-4535-9C81-3998DE215F3E}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{B3D50D8A-9A37-4170-AF81-F2D895D672B4}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{9724F171-C8B3-461C-991B-B894039640B2}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{CDF86598-607A-438E-AF22-4EEBA21ADDA8}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{A35CF3C6-3161-4635-9441-9329A26435B7}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{651F7062-9191-4ABA-BC6E-96CDA6B14D5C}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{F8481195-3B99-47D1-8AA0-D7C670DDE37C}"/>
+    <hyperlink ref="C21" r:id="rId20" xr:uid="{A157887B-51A6-4EF5-8147-28F7AC71DF6D}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{23FF6FA4-AFD8-47B9-B81E-B7EB0586D21B}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{BAF5F486-DDF1-4847-A5B0-FA2E772555BB}"/>
+    <hyperlink ref="C24" r:id="rId23" xr:uid="{1FB3EDC5-F9CF-4CA0-AE12-F60DBFFC1951}"/>
+    <hyperlink ref="C25" r:id="rId24" xr:uid="{C03164B7-067A-43BB-BA52-86621B0F18A3}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{AD1E22F5-276F-45F6-97A9-755B9585DE5B}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{9846C4FC-0F31-4A91-B1CA-A90F3D636E4C}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{979AA904-1B38-4DC1-9E77-BC9D0E40D7FD}"/>
+    <hyperlink ref="C29" r:id="rId28" xr:uid="{2ED64635-E712-4208-A863-2CF2C0A2A8A3}"/>
+    <hyperlink ref="C30" r:id="rId29" xr:uid="{F0A0BB6E-D34E-4088-A01E-A197A8CB25AE}"/>
+    <hyperlink ref="C31" r:id="rId30" xr:uid="{C2D239C9-BB00-4898-8435-C5F2FC287AB0}"/>
+    <hyperlink ref="C32" r:id="rId31" xr:uid="{5CE7A337-E930-4C61-B9BE-A5DDCF9AA2C7}"/>
+    <hyperlink ref="C33" r:id="rId32" xr:uid="{407ED8B0-02A0-4CC2-B873-EDBB5BAE5D28}"/>
+    <hyperlink ref="C34" r:id="rId33" xr:uid="{4F9BD2EE-03C7-4BA1-A160-64159AB5C0DE}"/>
+    <hyperlink ref="C35" r:id="rId34" xr:uid="{CA9BE976-B958-48A3-A37C-CE47D9717051}"/>
+    <hyperlink ref="C36" r:id="rId35" xr:uid="{EF1BD81E-551F-4C99-BBC7-07BF0385ECC8}"/>
+    <hyperlink ref="C37" r:id="rId36" xr:uid="{617A43B4-5A4D-4D04-A7B1-12415CF3ACB9}"/>
+    <hyperlink ref="C38" r:id="rId37" xr:uid="{593C8B63-7A2A-410D-A962-476B41EB21C3}"/>
+    <hyperlink ref="C39" r:id="rId38" xr:uid="{EF4CA06F-29BD-461E-8408-9C1719F4660B}"/>
+    <hyperlink ref="C40" r:id="rId39" xr:uid="{F6F571D3-A598-464D-A90B-9E356A55EAC2}"/>
+    <hyperlink ref="C41" r:id="rId40" xr:uid="{B4C1D491-5CF4-4352-84E6-92976755C6D2}"/>
+    <hyperlink ref="C42" r:id="rId41" xr:uid="{CAA33D11-5543-40CA-82E8-771D68BDB3E8}"/>
+    <hyperlink ref="C43" r:id="rId42" xr:uid="{6C596840-8300-4FE9-A5E5-F27F6FEEF965}"/>
+    <hyperlink ref="C44" r:id="rId43" xr:uid="{B7D1EBB8-057B-4E35-A1AE-B8BDF090144F}"/>
+    <hyperlink ref="C45" r:id="rId44" xr:uid="{6CB8E464-3F4B-4EFD-A131-E48C72268573}"/>
+    <hyperlink ref="C46" r:id="rId45" xr:uid="{9BC32D6C-1D92-4DFB-850E-ADB6AD192B09}"/>
+    <hyperlink ref="C47" r:id="rId46" xr:uid="{ADF9198D-5CA0-4D51-BDDC-73A35D59B9A1}"/>
+    <hyperlink ref="C48" r:id="rId47" xr:uid="{424A910B-C0BF-4DE7-8BB3-7AB09D93F71C}"/>
+    <hyperlink ref="C49" r:id="rId48" xr:uid="{082ACC80-9ABE-440D-9AF9-3A7B47A7BF99}"/>
+    <hyperlink ref="C50" r:id="rId49" xr:uid="{4D497EC2-E7B0-48E7-81CF-AE90DCD048C5}"/>
+    <hyperlink ref="C51" r:id="rId50" xr:uid="{CF78CFDE-A72F-4050-8CE8-C3D9428E9814}"/>
+    <hyperlink ref="C52" r:id="rId51" xr:uid="{902CFCB5-F420-4DEC-89ED-AA67E1494116}"/>
+    <hyperlink ref="C53" r:id="rId52" xr:uid="{1DBA5881-ABA8-44F1-B8BA-F4CACE1FBC21}"/>
+    <hyperlink ref="C54" r:id="rId53" xr:uid="{BCDF6EA1-F669-4CA6-A4D1-EC277B6CEE7E}"/>
+    <hyperlink ref="C55" r:id="rId54" xr:uid="{FF5D0271-3101-4FFE-B304-D03F6177E011}"/>
+    <hyperlink ref="C56" r:id="rId55" xr:uid="{522F9F4B-65AC-43F5-813A-A0B537C42CE9}"/>
+    <hyperlink ref="C57" r:id="rId56" xr:uid="{5C205FE0-373E-49F0-8A4F-40867A127E87}"/>
+    <hyperlink ref="C58" r:id="rId57" xr:uid="{DECC7003-06D5-4C36-9C65-62023877D59D}"/>
+    <hyperlink ref="C59" r:id="rId58" xr:uid="{720BE874-FD17-4B87-A383-4194929C14AE}"/>
+    <hyperlink ref="C60" r:id="rId59" xr:uid="{1C8A363A-D71A-43F7-A30D-A1EF49BB4830}"/>
+    <hyperlink ref="C61" r:id="rId60" xr:uid="{F668A1D5-DE6B-4C4A-AF83-F4EBFBFAC069}"/>
+    <hyperlink ref="C62" r:id="rId61" xr:uid="{7098ED43-DF14-44FD-BCCC-ADBA483054AA}"/>
+    <hyperlink ref="C63" r:id="rId62" xr:uid="{40C2E4CE-9AD7-476F-82FE-B4CBD002C790}"/>
+    <hyperlink ref="C64" r:id="rId63" xr:uid="{8927176B-86B2-4D97-9E02-28D0039FE795}"/>
+    <hyperlink ref="C65" r:id="rId64" xr:uid="{49B340E1-09F2-4E67-B57A-010FB8BDF231}"/>
+    <hyperlink ref="C66" r:id="rId65" xr:uid="{82DB2D12-9085-42C1-8A9F-41C20BFA1B5A}"/>
+    <hyperlink ref="C67" r:id="rId66" xr:uid="{393A9EA4-0A89-4B4F-A1B4-8A31EE34D99F}"/>
+    <hyperlink ref="C68" r:id="rId67" xr:uid="{B4B077EA-1516-427E-B517-2FEEAE11F26F}"/>
+    <hyperlink ref="C69" r:id="rId68" xr:uid="{4EEDF866-3CA2-4637-B05E-053B0FCCAD9D}"/>
+    <hyperlink ref="C70" r:id="rId69" xr:uid="{56B840C6-7AF5-455E-AED3-E1CE742CBD69}"/>
+    <hyperlink ref="C71" r:id="rId70" xr:uid="{5E1EB46A-CF84-46E2-9195-159DFD74E52B}"/>
+    <hyperlink ref="C72" r:id="rId71" xr:uid="{BC9EE5D6-F26C-4F2F-8197-4E59555DB51E}"/>
+    <hyperlink ref="C73" r:id="rId72" xr:uid="{AAB9CB18-C3A3-43EE-BE9B-FF82E9F4FCA2}"/>
+    <hyperlink ref="C74" r:id="rId73" xr:uid="{55F0A147-99EE-410D-843A-620EC94FF224}"/>
+    <hyperlink ref="C75" r:id="rId74" xr:uid="{4E310AC7-0235-4AD2-890F-5A439A029550}"/>
+    <hyperlink ref="C76" r:id="rId75" xr:uid="{17F3A6AB-E17A-4DBC-9F45-AB0F9A7D7FB6}"/>
+    <hyperlink ref="C77" r:id="rId76" xr:uid="{8AEB1020-B1C1-49B7-B567-CE67BF47EEC6}"/>
+    <hyperlink ref="C78" r:id="rId77" xr:uid="{4BA480A9-7238-4B07-942F-21109E610F27}"/>
+    <hyperlink ref="C79" r:id="rId78" xr:uid="{ACFFB77E-B99F-4454-92E1-A7A35EB0FEA1}"/>
+    <hyperlink ref="C80" r:id="rId79" xr:uid="{07728ABD-2779-4654-A1B9-830D2802FCAC}"/>
+    <hyperlink ref="C81" r:id="rId80" xr:uid="{C4A18212-C1F8-41B2-B2EF-09AF33CFBDD7}"/>
+    <hyperlink ref="C82" r:id="rId81" xr:uid="{72A92F2A-8CB3-4EA6-A3A1-DDFD9C25DAD2}"/>
+    <hyperlink ref="C83" r:id="rId82" xr:uid="{DC03474A-E59A-4D50-8CF7-AFC4DA548586}"/>
+    <hyperlink ref="C84" r:id="rId83" xr:uid="{63402EC3-D95A-486E-9082-2FC322009615}"/>
+    <hyperlink ref="C85" r:id="rId84" xr:uid="{92EDB1D4-F5CE-4C0D-9C57-D444C0139042}"/>
+    <hyperlink ref="C86" r:id="rId85" xr:uid="{7A32FE96-0802-4925-97F7-04F48DA3CA85}"/>
+    <hyperlink ref="C87" r:id="rId86" xr:uid="{176E127C-C998-4D1B-A5EB-CCF3AB64E89D}"/>
+    <hyperlink ref="C88" r:id="rId87" xr:uid="{47E3532C-40E8-4BC8-80A6-FBAECA3B980C}"/>
+    <hyperlink ref="C89" r:id="rId88" xr:uid="{2CDCF889-93CC-44D8-9AAC-CFEE717095ED}"/>
+    <hyperlink ref="C90" r:id="rId89" xr:uid="{58C2DCA4-03B5-4E5E-9B04-3DA1C415E768}"/>
+    <hyperlink ref="C91" r:id="rId90" xr:uid="{74AA213A-557C-4370-B3B6-330BA72EBF57}"/>
+    <hyperlink ref="C92" r:id="rId91" xr:uid="{A500F965-A07F-468C-9D07-BA835C857D5B}"/>
+    <hyperlink ref="C93" r:id="rId92" xr:uid="{7023BDE2-A348-4C1F-A7B4-E2AE5A543800}"/>
+    <hyperlink ref="C94" r:id="rId93" xr:uid="{215A8CE1-BDAD-40FB-9B36-CF09662C1D4E}"/>
+    <hyperlink ref="C95" r:id="rId94" xr:uid="{BB062A2D-9F94-4487-AAE4-66A80DDC7E19}"/>
+    <hyperlink ref="C96" r:id="rId95" xr:uid="{01BDBCE6-5881-49B2-A900-025A234B538D}"/>
+    <hyperlink ref="C97" r:id="rId96" xr:uid="{670F066A-723D-4753-B45C-D2DAA11C4CFA}"/>
+    <hyperlink ref="C98" r:id="rId97" xr:uid="{A08128D6-79FD-425D-B854-6B0E97B55FFA}"/>
+    <hyperlink ref="C99" r:id="rId98" xr:uid="{19C6DAA8-C5A6-468B-9489-9070007A0C6F}"/>
+    <hyperlink ref="C100" r:id="rId99" xr:uid="{09E5E895-F3C0-4345-983F-6ADDEBD3FF2B}"/>
+    <hyperlink ref="C101" r:id="rId100" xr:uid="{BB2F148C-4AB0-4956-AE18-E0244D7B5C95}"/>
+    <hyperlink ref="C102" r:id="rId101" xr:uid="{262B5057-2373-41C6-B75A-03235E9B6470}"/>
+    <hyperlink ref="C103" r:id="rId102" xr:uid="{4B365BEE-E2ED-4910-9263-5DBFD53475DC}"/>
+    <hyperlink ref="C104" r:id="rId103" xr:uid="{030651CC-F34D-4891-89A6-511B3641DF0B}"/>
+    <hyperlink ref="C105" r:id="rId104" xr:uid="{60D2EEB8-815C-4BA3-9A0C-0D6EFD12D3D0}"/>
+    <hyperlink ref="C106" r:id="rId105" xr:uid="{05A62BB8-4024-427D-A702-8A5A987D5704}"/>
+    <hyperlink ref="C107" r:id="rId106" xr:uid="{94B86E60-DF0D-41B8-ACEB-191B8C5CBAFE}"/>
+    <hyperlink ref="C108" r:id="rId107" xr:uid="{591D8108-0AA8-470A-8B13-49E2ABF52D2F}"/>
+    <hyperlink ref="C109" r:id="rId108" xr:uid="{20BFBFFD-9781-4FF9-80B4-0B0A23073D79}"/>
+    <hyperlink ref="C110" r:id="rId109" xr:uid="{791C3095-0A98-42BF-A8F9-686BF3F95EED}"/>
+    <hyperlink ref="C111" r:id="rId110" xr:uid="{01D9C697-02C2-49A1-8365-D1C19652BB28}"/>
+    <hyperlink ref="C112" r:id="rId111" xr:uid="{18E48382-B454-4AFC-A465-A90FCF2CE5D6}"/>
+    <hyperlink ref="C113" r:id="rId112" xr:uid="{7BEC6D7E-998F-4807-B17D-072615913695}"/>
+    <hyperlink ref="C114" r:id="rId113" xr:uid="{63310BFF-299E-4675-8473-3F5852B96FBE}"/>
+    <hyperlink ref="C115" r:id="rId114" xr:uid="{F2C68036-ED87-4899-A4CC-D489FF53469A}"/>
+    <hyperlink ref="C116" r:id="rId115" xr:uid="{0AA3AC92-640F-4EA2-852E-6A229279A1BF}"/>
+    <hyperlink ref="C117" r:id="rId116" xr:uid="{A155A2B1-6319-40E3-AFEE-F4AF262F1E77}"/>
+    <hyperlink ref="C118" r:id="rId117" xr:uid="{E6851CBD-BECF-4C6C-9D73-7E5F57658EAE}"/>
+    <hyperlink ref="C119" r:id="rId118" xr:uid="{DAF82B7A-567A-408C-B903-F7313E792535}"/>
+    <hyperlink ref="C120" r:id="rId119" xr:uid="{E43B7AF9-27F9-4340-909F-15341DA63328}"/>
+    <hyperlink ref="C121" r:id="rId120" xr:uid="{5A34897C-8D0E-4841-9ACD-A560ACFA937F}"/>
+    <hyperlink ref="C122" r:id="rId121" xr:uid="{34C2086C-20CA-4E56-A8EF-D816FD042321}"/>
+    <hyperlink ref="C123" r:id="rId122" xr:uid="{1E750F40-65AB-4B41-8999-04A7FFA4CF76}"/>
+    <hyperlink ref="C124" r:id="rId123" xr:uid="{CD29C1F7-B759-459E-A959-493C31FC0C14}"/>
+    <hyperlink ref="C125" r:id="rId124" xr:uid="{92019009-7A0B-4EEF-B5A3-D0288E624BC3}"/>
+    <hyperlink ref="C126" r:id="rId125" xr:uid="{E4DECFB6-DFC2-4F6E-9490-C6EAD73E5BF0}"/>
+    <hyperlink ref="C127" r:id="rId126" xr:uid="{2ED4296E-976B-405A-AC77-0AFDCBCBCF57}"/>
+    <hyperlink ref="C128" r:id="rId127" xr:uid="{FFA37B44-9C4A-4EE1-96A9-CDA875E6536F}"/>
+    <hyperlink ref="C129" r:id="rId128" xr:uid="{B6BA643D-04E0-4AAA-8E04-D210EAA692FE}"/>
+    <hyperlink ref="C130" r:id="rId129" xr:uid="{AB0EE9A0-F661-4148-99F6-0D526FDDF0DC}"/>
+    <hyperlink ref="C131" r:id="rId130" xr:uid="{0EB68027-A64A-42E4-B325-39D8E21C377F}"/>
+    <hyperlink ref="C132" r:id="rId131" xr:uid="{AA96E6C5-07EF-45BD-A4D2-A932FFD52488}"/>
+    <hyperlink ref="C133" r:id="rId132" xr:uid="{D87C9431-A637-4466-B77C-A981E8537B79}"/>
+    <hyperlink ref="C134" r:id="rId133" xr:uid="{F4DE2DED-2973-4BEB-ABC3-E51630049872}"/>
+    <hyperlink ref="C135" r:id="rId134" xr:uid="{236B9999-8840-4BD7-9197-3B427E126880}"/>
+    <hyperlink ref="C136" r:id="rId135" xr:uid="{58690B99-7ED7-4524-B464-17C6436E95B8}"/>
+    <hyperlink ref="C137" r:id="rId136" xr:uid="{6D4222F3-5D59-4E44-A708-974282E6184F}"/>
+    <hyperlink ref="C138" r:id="rId137" xr:uid="{D5C2803D-21ED-4D45-9B28-10871784E77B}"/>
+    <hyperlink ref="C139" r:id="rId138" xr:uid="{F2143C4A-B988-48F5-B6B8-0986B2CE8F43}"/>
+    <hyperlink ref="C140" r:id="rId139" xr:uid="{EFB1426D-6706-47B2-8AB3-C554E2512B13}"/>
+    <hyperlink ref="C141" r:id="rId140" xr:uid="{224D0D1E-E293-47C7-9A18-B15C0BF3205B}"/>
+    <hyperlink ref="C142" r:id="rId141" xr:uid="{0C7200DB-24C4-4F61-98A3-114BFB5A63DB}"/>
+    <hyperlink ref="C143" r:id="rId142" xr:uid="{A1D5A839-4D23-4056-A648-E0C7C34E9402}"/>
+    <hyperlink ref="C144" r:id="rId143" xr:uid="{4C8613D1-9643-41B5-B348-7BCF2F317A63}"/>
+    <hyperlink ref="C145" r:id="rId144" xr:uid="{523549E6-B30A-4241-8638-29E9975CCFCC}"/>
+    <hyperlink ref="C146" r:id="rId145" xr:uid="{0E4149F8-34D2-4446-9A23-DE1114C8DFA9}"/>
+    <hyperlink ref="C147" r:id="rId146" xr:uid="{B3525A61-DFF7-47C9-9456-031684B927BD}"/>
+    <hyperlink ref="C148" r:id="rId147" xr:uid="{2E5332BD-2C3A-4B87-913A-8925E8397411}"/>
+    <hyperlink ref="C149" r:id="rId148" xr:uid="{59C68014-4602-46ED-BA81-61AFC84EC80C}"/>
+    <hyperlink ref="C150" r:id="rId149" xr:uid="{B087CA4E-89F7-498C-9067-DC8A69A55130}"/>
+    <hyperlink ref="C151" r:id="rId150" xr:uid="{EA3F454E-7CB1-47AD-8BE1-3AB427F2140E}"/>
+    <hyperlink ref="C153" r:id="rId151" xr:uid="{DB3D0653-8E10-472F-A00E-3E5815AD55F9}"/>
+    <hyperlink ref="C154" r:id="rId152" xr:uid="{EE4FDD65-1488-4739-82FE-AD8D60304EDA}"/>
+    <hyperlink ref="C152" r:id="rId153" xr:uid="{50BFFA72-2E37-44DB-B912-70A2B717E99E}"/>
+    <hyperlink ref="C155" r:id="rId154" xr:uid="{6DE20993-2291-4AF5-BE1F-109F2C1E4569}"/>
+    <hyperlink ref="C156" r:id="rId155" xr:uid="{F6FF826D-AD8D-40F4-B366-04F89051B3CE}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId156"/>
 </worksheet>
 </file>